--- a/data/trans_bre/P15-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P15-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,58; -2,55</t>
+          <t>-9,32; -2,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -1,83</t>
+          <t>-9,94; -1,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,46; -2,25</t>
+          <t>-9,52; -2,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 7,26</t>
+          <t>-3,55; 7,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,54; -28,17</t>
+          <t>-73,52; -28,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,24; -13,86</t>
+          <t>-64,13; -15,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-74,33; -24,57</t>
+          <t>-74,54; -26,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,93; 331,87</t>
+          <t>-53,02; 358,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -0,38</t>
+          <t>-6,1; -0,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,9; -2,34</t>
+          <t>-8,76; -2,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -1,45</t>
+          <t>-7,45; -1,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -0,4</t>
+          <t>-7,64; -0,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,56; -1,26</t>
+          <t>-60,33; -4,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,54; -21,64</t>
+          <t>-62,38; -21,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,75; -20,95</t>
+          <t>-72,02; -25,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,06; -4,62</t>
+          <t>-81,52; -5,84</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,82</t>
+          <t>-7,28; -2,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,8; -1,62</t>
+          <t>-7,03; -1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,76</t>
+          <t>-4,01; 0,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,79</t>
+          <t>-4,54; 0,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,51; -27,66</t>
+          <t>-77,49; -35,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,26; -22,03</t>
+          <t>-68,86; -21,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-58,79; 23,17</t>
+          <t>-61,99; 23,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,91; 18,19</t>
+          <t>-52,5; 17,72</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -1,24</t>
+          <t>-7,08; -0,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,59</t>
+          <t>-2,9; 2,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,65</t>
+          <t>-3,08; 1,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 2,64</t>
+          <t>-4,69; 2,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,37; -16,87</t>
+          <t>-73,05; -13,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 57,08</t>
+          <t>-39,8; 61,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,15; 51,73</t>
+          <t>-54,21; 53,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,6; 88,56</t>
+          <t>-56,58; 67,53</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,41</t>
+          <t>-3,74; 2,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 10,06</t>
+          <t>2,92; 9,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 6,18</t>
+          <t>0,45; 6,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,47</t>
+          <t>-1,25; 3,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 72,77</t>
+          <t>-53,85; 69,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,84; 553,28</t>
+          <t>59,71; 555,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 336,28</t>
+          <t>6,05; 346,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 84,69</t>
+          <t>-21,43; 96,89</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 7,47</t>
+          <t>0,62; 7,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,39</t>
+          <t>-2,38; 4,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 7,78</t>
+          <t>1,28; 7,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 4,79</t>
+          <t>-3,12; 4,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,83; 358,3</t>
+          <t>4,76; 299,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,44; 157,72</t>
+          <t>-32,89; 133,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,11; 385,89</t>
+          <t>20,18; 378,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 123,24</t>
+          <t>-53,54; 134,53</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 10,38</t>
+          <t>1,56; 10,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 10,19</t>
+          <t>-0,52; 10,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 8,35</t>
+          <t>0,04; 9,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,7</t>
+          <t>1,88; 8,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,8; 465,03</t>
+          <t>14,25; 417,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 179,12</t>
+          <t>-7,26; 169,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 199,61</t>
+          <t>-2,15; 221,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,56; 162,37</t>
+          <t>22,41; 154,65</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -1,03</t>
+          <t>-3,42; -1,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,03</t>
+          <t>-2,26; 0,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,69</t>
+          <t>-1,67; 0,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,57</t>
+          <t>-1,37; 1,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,52; -14,97</t>
+          <t>-42,74; -15,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 0,51</t>
+          <t>-25,06; 2,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 13,38</t>
+          <t>-26,6; 11,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 30,97</t>
+          <t>-21,49; 31,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P15-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P15-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -2,61</t>
+          <t>-9,61; -2,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -1,79</t>
+          <t>-9,55; -1,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,52; -2,54</t>
+          <t>-9,75; -2,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 7,16</t>
+          <t>-4,48; 6,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,52; -28,1</t>
+          <t>-73,55; -31,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-64,13; -15,77</t>
+          <t>-63,44; -16,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-74,54; -26,59</t>
+          <t>-75,38; -25,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 358,7</t>
+          <t>-60,92; 204,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-3,9</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-54,53%</t>
+          <t>-56,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -0,46</t>
+          <t>-5,93; -0,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,76; -2,28</t>
+          <t>-9,0; -2,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -1,86</t>
+          <t>-7,31; -1,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,64; -0,29</t>
+          <t>-7,99; -0,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,33; -4,66</t>
+          <t>-56,86; -1,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -21,27</t>
+          <t>-64,46; -20,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,02; -25,86</t>
+          <t>-70,72; -24,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,52; -5,84</t>
+          <t>-79,24; -7,85</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-1,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-25,09%</t>
+          <t>-21,13%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -2,31</t>
+          <t>-6,97; -1,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,03; -1,49</t>
+          <t>-7,26; -1,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,91</t>
+          <t>-3,95; 0,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,74</t>
+          <t>-4,06; 0,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,49; -35,72</t>
+          <t>-77,77; -32,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,86; -21,51</t>
+          <t>-69,97; -24,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-61,99; 23,86</t>
+          <t>-59,78; 17,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 17,72</t>
+          <t>-51,98; 18,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-27,82%</t>
+          <t>-44,56%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -0,91</t>
+          <t>-7,3; -1,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,76</t>
+          <t>-3,0; 2,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,65</t>
+          <t>-2,9; 1,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,21</t>
+          <t>-6,08; -0,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,05; -13,63</t>
+          <t>-74,17; -19,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 61,29</t>
+          <t>-40,43; 54,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,21; 53,64</t>
+          <t>-53,17; 43,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,58; 67,53</t>
+          <t>-60,87; -14,3</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,12</t>
+          <t>-3,48; 2,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,43</t>
+          <t>3,15; 10,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,04</t>
+          <t>0,57; 6,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,73</t>
+          <t>-1,64; 3,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 69,0</t>
+          <t>-54,28; 66,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,71; 555,0</t>
+          <t>61,41; 516,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 346,4</t>
+          <t>12,01; 340,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 96,89</t>
+          <t>-24,84; 77,68</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,4</t>
+          <t>0,59; 7,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,97</t>
+          <t>-2,35; 5,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,78</t>
+          <t>1,51; 8,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 4,78</t>
+          <t>1,33; 6,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 299,95</t>
+          <t>1,31; 343,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 133,35</t>
+          <t>-33,07; 142,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,18; 378,32</t>
+          <t>23,53; 372,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 134,53</t>
+          <t>19,68; 190,3</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>64,37%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 10,25</t>
+          <t>1,65; 10,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 10,21</t>
+          <t>-0,4; 10,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 9,04</t>
+          <t>-0,13; 9,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,2</t>
+          <t>1,47; 7,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,25; 417,39</t>
+          <t>18,85; 448,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 169,34</t>
+          <t>-6,72; 158,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 221,03</t>
+          <t>-3,08; 231,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,41; 154,65</t>
+          <t>14,77; 137,66</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>-0,65%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -1,04</t>
+          <t>-3,4; -1,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,18</t>
+          <t>-2,56; 0,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,6</t>
+          <t>-1,53; 0,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,55</t>
+          <t>-1,14; 1,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,74; -15,09</t>
+          <t>-42,0; -15,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 2,46</t>
+          <t>-28,57; 1,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 11,55</t>
+          <t>-24,2; 10,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 31,86</t>
+          <t>-16,53; 19,23</t>
         </is>
       </c>
     </row>
